--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.63421573437047</v>
+        <v>12.1280600568352</v>
       </c>
       <c r="D2" t="n">
-        <v>109.3421070621178</v>
+        <v>17.76809239759415</v>
       </c>
       <c r="E2" t="n">
-        <v>17.24385548274718</v>
+        <v>2.802126515946417</v>
       </c>
       <c r="F2" t="n">
-        <v>32.43919839034574</v>
+        <v>5.271369738431184</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.83987465470972</v>
+        <v>5.336479631390329</v>
       </c>
       <c r="D3" t="n">
-        <v>33.53448215063393</v>
+        <v>5.449353349478013</v>
       </c>
       <c r="E3" t="n">
-        <v>17.24385548274718</v>
+        <v>2.802126515946417</v>
       </c>
       <c r="F3" t="n">
-        <v>32.43919839034574</v>
+        <v>5.271369738431184</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.44532771510575</v>
+        <v>7.872365753704686</v>
       </c>
       <c r="D4" t="n">
-        <v>50.81645742108203</v>
+        <v>8.25767433092583</v>
       </c>
       <c r="E4" t="n">
-        <v>17.24385548274718</v>
+        <v>2.802126515946417</v>
       </c>
       <c r="F4" t="n">
-        <v>32.43919839034574</v>
+        <v>5.271369738431184</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
